--- a/out/policy_events_2026-10-13.xlsx
+++ b/out/policy_events_2026-10-13.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I35"/>
+  <dimension ref="A1:I37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,22 +508,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>구리값 웃돈에 美로 물량 집중…트럼프 관세 딜레마 - 한국경제</t>
+          <t>[단독] 삼성·SK 美공장 건설비 부담 커질라…美 반도체업계 "관세 낮춰라" 요구 - 뉴스핌</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>구리값 웃돈에 美로 물량 집중…트럼프 관세 딜레마&amp;nbsp;&amp;nbsp;한국경제</t>
+          <t>[단독] 삼성·SK 美공장 건설비 부담 커질라…美 반도체업계 "관세 낮춰라" 요구&amp;nbsp;&amp;nbsp;뉴스핌</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 23:24:05 GMT</t>
+          <t>Tue, 13 Oct 2026 05:25:00 GMT</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBLQjJadFlzcXpHWkZCY0NBakhGZUN5WkEzLTBTNkFxUmtpckF1V0JZbmtGR3hGbzg2V2FWVVhxMFpkeVRDR01sWHhZVmgxNTJZMTduejluTE5EZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9NZkxLLUV5amhyMjd6b1kzWGZRbFkwaWpwdEJRVEZYek1HU3dvT2pqWlJTb01Td1pMekE2QkNRODkwcFVLaE14c3ZhcVR5cG1XdlNUS1ZHdkZJSXJx?oc=5</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -533,7 +533,7 @@
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I3" t="inlineStr"/>
     </row>
@@ -545,32 +545,32 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>충북FTA통상진흥센터, 수출기업 통상·관세 애로 해소 - 충청매일</t>
+          <t>구리값 웃돈에 美로 물량 집중…트럼프 관세 딜레마 - 한국경제</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>충북FTA통상진흥센터, 수출기업 통상·관세 애로 해소&amp;nbsp;&amp;nbsp;충청매일</t>
+          <t>구리값 웃돈에 美로 물량 집중…트럼프 관세 딜레마&amp;nbsp;&amp;nbsp;한국경제</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 10:00:25 GMT</t>
+          <t>Mon, 12 Oct 2026 23:24:05 GMT</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBDa1I1aU9EMGZiLTdKbkVMbXRTNXc2bkhMeVFyb29FOEVRaEhSZUhJRjFFV2d3bEpxYVg3cnQ5aFFkRk5JSVVvYkg3Qk4yelNHYi1zVDkyc055Y3o2T09XTXlkanRvZklhUlE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiWkFVX3lxTFBLQjJadFlzcXpHWkZCY0NBakhGZUN5WkEzLTBTNkFxUmtpckF1V0JZbmtGR3hGbzg2V2FWVVhxMFpkeVRDR01sWHhZVmgxNTJZMTduejluTE5EZw?oc=5</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I4" t="inlineStr"/>
     </row>
@@ -582,32 +582,32 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>[단독] 삼성·SK 美공장 건설비 부담 커질라…美 반도체업계 "관세 낮춰라" 요구 - 뉴스핌</t>
+          <t>충북FTA통상진흥센터, 수출기업 통상·관세 애로 해소 - 충청매일</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[단독] 삼성·SK 美공장 건설비 부담 커질라…美 반도체업계 "관세 낮춰라" 요구&amp;nbsp;&amp;nbsp;뉴스핌</t>
+          <t>충북FTA통상진흥센터, 수출기업 통상·관세 애로 해소&amp;nbsp;&amp;nbsp;충청매일</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:25:00 GMT</t>
+          <t>Tue, 13 Oct 2026 10:00:25 GMT</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiXEFVX3lxTE9NZkxLLUV5amhyMjd6b1kzWGZRbFkwaWpwdEJRVEZYek1HU3dvT2pqWlJTb01Td1pMekE2QkNRODkwcFVLaE14c3ZhcVR5cG1XdlNUS1ZHdkZJSXJx?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTFBDa1I1aU9EMGZiLTdKbkVMbXRTNXc2bkhMeVFyb29FOEVRaEhSZUhJRjFFV2d3bEpxYVg3cnQ5aFFkRk5JSVVvYkg3Qk4yelNHYi1zVDkyc055Y3o2T09XTXlkanRvZklhUlE?oc=5</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I5" t="inlineStr"/>
     </row>
@@ -767,22 +767,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>[오늘의 경제뉴스] 안에선 중국산 공세, 밖에선 미국 관세…철강업계 회복세 ‘찬물’ - 뉴스버스</t>
+          <t>포항상의, 경주서 수출 설명회 개최…EU 환경규제·미국 관세 대응 전략 공유 - 브레이크뉴스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[오늘의 경제뉴스] 안에선 중국산 공세, 밖에선 미국 관세…철강업계 회복세 ‘찬물’&amp;nbsp;&amp;nbsp;뉴스버스</t>
+          <t>포항상의, 경주서 수출 설명회 개최…EU 환경규제·미국 관세 대응 전략 공유&amp;nbsp;&amp;nbsp;브레이크뉴스</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 16:57:15 GMT</t>
+          <t>Tue, 13 Oct 2026 06:12:51 GMT</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1EUU9icTRaVlN3c2FmQzdnSGtoY3RLRGlSUk12ZDI4dTJURFFTOHJfd2g1UXFQUV91bmxVTHVSTFd6R1dkVWNMdHJHZHBXaEdmZUxldjQ1Ul9qdU5idElyYXd1a1RtOXZfWnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiQkFVX3lxTE0wbHZvMnBZSG16c3NCd19vS053cWtrR0RvLTBFMV9VOHpTNFpTNGM3c1F0VnZOSlNuRXFuMGFmWnpIQQ?oc=5</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -792,7 +792,7 @@
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" t="inlineStr"/>
     </row>
@@ -804,22 +804,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>포항상의, 경주서 수출 설명회 개최…EU 환경규제·미국 관세 대응 전략 공유 - 브레이크뉴스</t>
+          <t>[오늘의 경제뉴스] 안에선 중국산 공세, 밖에선 미국 관세…철강업계 회복세 ‘찬물’ - 뉴스버스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>포항상의, 경주서 수출 설명회 개최…EU 환경규제·미국 관세 대응 전략 공유&amp;nbsp;&amp;nbsp;브레이크뉴스</t>
+          <t>[오늘의 경제뉴스] 안에선 중국산 공세, 밖에선 미국 관세…철강업계 회복세 ‘찬물’&amp;nbsp;&amp;nbsp;뉴스버스</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 06:12:51 GMT</t>
+          <t>Mon, 12 Oct 2026 16:57:15 GMT</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiQkFVX3lxTE0wbHZvMnBZSG16c3NCd19vS053cWtrR0RvLTBFMV9VOHpTNFpTNGM3c1F0VnZOSlNuRXFuMGFmWnpIQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE1EUU9icTRaVlN3c2FmQzdnSGtoY3RLRGlSUk12ZDI4dTJURFFTOHJfd2g1UXFQUV91bmxVTHVSTFd6R1dkVWNMdHJHZHBXaEdmZUxldjQ1Ul9qdU5idElyYXd1a1RtOXZfWnc?oc=5</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I11" t="inlineStr"/>
     </row>
@@ -851,7 +851,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 01:32:18 GMT</t>
+          <t>Tue, 13 Oct 2026 01:32:00 GMT</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -989,22 +989,22 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>포항상공회의소 경북동부FTA통상진흥센터, 2026년 찾아가는 수출 설명회 in 경주 - 경북도민일보</t>
+          <t>충북FTA통상진흥센터, 2026 찾아가는 FTA·통상데스크 개최 - 충북일보</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>포항상공회의소 경북동부FTA통상진흥센터, 2026년 찾아가는 수출 설명회 in 경주&amp;nbsp;&amp;nbsp;경북도민일보</t>
+          <t>충북FTA통상진흥센터, 2026 찾아가는 FTA·통상데스크 개최&amp;nbsp;&amp;nbsp;충북일보</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 10:05:45 GMT</t>
+          <t>Tue, 13 Oct 2026 07:42:45 GMT</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5xbzlRTk5jVFNVSXJsUXk4YlgwbVJXM1hfRkNBcW1aUlFGcHN3RjhMYTFuRklETXBmRTZ2S0M0UXgyUUMycWpLNGFyTkFFSnBLeW9vMFBIdUZEU001YkV0d1p6clR5M1lOLUE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiYkFVX3lxTE9BZDhkbW14VUw5b00wRXpESUkxUklBelpkdHBBZG1FZGwzMTJnS3N4dUtWZnNsNy1aVGEweDhyS256ckd0YVBZU3oxTGVZLWdiNjY1d0tLaWdYd2VHV0R5Mnhn?oc=5</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>충북 수출기업, FTA·통상 대응 실무 지원 - 충청도민일보</t>
+          <t>포항상공회의소 경북동부FTA통상진흥센터, 2026년 찾아가는 수출 설명회 in 경주 - 경북도민일보</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>충북 수출기업, FTA·통상 대응 실무 지원&amp;nbsp;&amp;nbsp;충청도민일보</t>
+          <t>포항상공회의소 경북동부FTA통상진흥센터, 2026년 찾아가는 수출 설명회 in 경주&amp;nbsp;&amp;nbsp;경북도민일보</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 08:54:44 GMT</t>
+          <t>Tue, 13 Oct 2026 10:05:45 GMT</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE0wS3RxT1JOZGJuTG9HNDFqdGdRMVI5OWQwbWQtdkVsUTNaNGN5Y2I5bGVITlpVWUR2ZWJfRkNQQ3BtQkd0WWZadHhqNWh2Zm55a0w1M3dhc0hudHBtT2tPZWpxM0lUNzFWLXpWMQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE5xbzlRTk5jVFNVSXJsUXk4YlgwbVJXM1hfRkNBcW1aUlFGcHN3RjhMYTFuRklETXBmRTZ2S0M0UXgyUUMycWpLNGFyTkFFSnBLeW9vMFBIdUZEU001YkV0d1p6clR5M1lOLUE?oc=5</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1359,32 +1359,32 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>EVFTA(유럽연합-브라질 자유무역협정)에 따른 원산지 규정 활용이 둔화되고 있다. - Vietnam.vn</t>
+          <t>김장철 절임배추 원산지 표시 집중 지도·점검 - 데일리저널</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>EVFTA(유럽연합-브라질 자유무역협정)에 따른 원산지 규정 활용이 둔화되고 있다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>김장철 절임배추 원산지 표시 집중 지도·점검&amp;nbsp;&amp;nbsp;데일리저널</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 04:48:47 GMT</t>
+          <t>Tue, 13 Oct 2026 06:02:23 GMT</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPTEtUZlVQVzZPUTFLcnNNWlltTHFybS1uaDJqRG5mVTNTN2dMSVVzWllGYTd6Z1NzTTZmWG1DNDJzSnN5dDJNb1FoZ0dtNUdfa2JNNTBXYms4VjVzXzV0b3JQLVY1cVZ5bXdwTWdZMDJZYUR1dV9JYURCUHJvb0MtMFh3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE9UYlhaNGFEWnVKSUl0cmdwVE43UUpEdzVoclFkcHBOR2FobVVnd29ra1JJbWpSdEVLeFpIalNoNF9uQ0c3Y01KWkZRX0JVWUxzNHJPR3VlUGM5cy1SM1k5WW5aT2NISTdTYWc?oc=5</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I26" t="inlineStr"/>
     </row>
@@ -1396,32 +1396,32 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>믿고 샀는데…하나로마트 등 원산지 표시 위반 - 메디컬투데이</t>
+          <t>EVFTA(유럽연합-브라질 자유무역협정)에 따른 원산지 규정 활용이 둔화되고 있다. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>믿고 샀는데…하나로마트 등 원산지 표시 위반&amp;nbsp;&amp;nbsp;메디컬투데이</t>
+          <t>EVFTA(유럽연합-브라질 자유무역협정)에 따른 원산지 규정 활용이 둔화되고 있다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 01:45:04 GMT</t>
+          <t>Tue, 13 Oct 2026 04:48:47 GMT</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1Oc29TSGJpcUVRNl9TUUo5MjBPV2x6VUtDSGttVE5XMlJjUFl1ZVgtbHVKOHlwR2NYejlmN1BMTS1lemluelVxNTNHZGVUV2N0bUJoS2ZQUjlxOWh3blVWWlBLVGZjaUxpdEZsaQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxPTEtUZlVQVzZPUTFLcnNNWlltTHFybS1uaDJqRG5mVTNTN2dMSVVzWllGYTd6Z1NzTTZmWG1DNDJzSnN5dDJNb1FoZ0dtNUdfa2JNNTBXYms4VjVzXzV0b3JQLVY1cVZ5bXdwTWdZMDJZYUR1dV9JYURCUHJvb0MtMFh3?oc=5</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="I27" t="inlineStr"/>
     </row>
@@ -1433,22 +1433,22 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>이양수 의원 "농협 판매장 원산지 위반 62건…강원 44건" - 전국매일신문</t>
+          <t>믿고 샀는데…하나로마트 등 원산지 표시 위반 - 메디컬투데이</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>이양수 의원 "농협 판매장 원산지 위반 62건…강원 44건"&amp;nbsp;&amp;nbsp;전국매일신문</t>
+          <t>믿고 샀는데…하나로마트 등 원산지 표시 위반&amp;nbsp;&amp;nbsp;메디컬투데이</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:27:11 GMT</t>
+          <t>Tue, 13 Oct 2026 01:45:04 GMT</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1xaVdHQXAwSTFBUWtyUjVHVFByaEpxY24zRnJNRGVsS25XamduYXIzWk5vYnpWVGJiS1dsVGlSTVhhX2dadk1Ra0FIQ1FPS2h0Q0FVaGZPU09OZVJWZlVIRVcxR0xUeFo2WmxsODFR?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE1Oc29TSGJpcUVRNl9TUUo5MjBPV2x6VUtDSGttVE5XMlJjUFl1ZVgtbHVKOHlwR2NYejlmN1BMTS1lemluelVxNTNHZGVUV2N0bUJoS2ZQUjlxOWh3blVWWlBLVGZjaUxpdEZsaQ?oc=5</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1470,22 +1470,22 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>우리 농산물 지킨다던 농협의 민낯… 5년간 62개 판매장에서 원산지 위반 '철퇴' - 청년투데이</t>
+          <t>이양수 의원 "농협 판매장 원산지 위반 62건…강원 44건" - 전국매일신문</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>우리 농산물 지킨다던 농협의 민낯… 5년간 62개 판매장에서 원산지 위반 '철퇴'&amp;nbsp;&amp;nbsp;청년투데이</t>
+          <t>이양수 의원 "농협 판매장 원산지 위반 62건…강원 44건"&amp;nbsp;&amp;nbsp;전국매일신문</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 02:06:15 GMT</t>
+          <t>Tue, 13 Oct 2026 05:27:11 GMT</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE4ta3dqendaeHhDU3ExLWpsYnk2SE5XVmVDMG5ZZ3lBRzBUYlJpQUtIWFY1RzRXa0NsVmtNRGpqal9yREF2THI1R21GQUYwTTd1ZHphUU1XRHdtWFVLd25PZUNJU1BnUXhib1E?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE1xaVdHQXAwSTFBUWtyUjVHVFByaEpxY24zRnJNRGVsS25XamduYXIzWk5vYnpWVGJiS1dsVGlSTVhhX2dadk1Ra0FIQ1FPS2h0Q0FVaGZPU09OZVJWZlVIRVcxR0xUeFo2WmxsODFR?oc=5</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1507,22 +1507,22 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>[국민청원] "식품 원산지 인증제 폐지 반대" - 전국매일신문</t>
+          <t>우리 농산물 지킨다던 농협의 민낯… 5년간 62개 판매장에서 원산지 위반 '철퇴' - 청년투데이</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>[국민청원] "식품 원산지 인증제 폐지 반대"&amp;nbsp;&amp;nbsp;전국매일신문</t>
+          <t>우리 농산물 지킨다던 농협의 민낯… 5년간 62개 판매장에서 원산지 위반 '철퇴'&amp;nbsp;&amp;nbsp;청년투데이</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:40:19 GMT</t>
+          <t>Tue, 13 Oct 2026 02:06:15 GMT</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5kemRCZFZJQXppYUlTRmRCeTFLeGg3SklTbzNub1pVRlNPYUhjOUhWd1h4MlI2d3J5X2JMZ1ZydFBJVW1NV05Bb29IZXd2SGNlNmdiVDQzR3l5V0dnbnh2bjJYZkZuWVdhbEdmOXJn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiakFVX3lxTE4ta3dqendaeHhDU3ExLWpsYnk2SE5XVmVDMG5ZZ3lBRzBUYlJpQUtIWFY1RzRXa0NsVmtNRGpqal9yREF2THI1R21GQUYwTTd1ZHphUU1XRHdtWFVLd25PZUNJU1BnUXhib1E?oc=5</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1544,32 +1544,32 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>VIFTA 활용: 기업은 원산지 규정을 적극적으로 준수해야 합니다. - Vietnam.vn</t>
+          <t>[국민청원] "식품 원산지 인증제 폐지 반대" - 전국매일신문</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VIFTA 활용: 기업은 원산지 규정을 적극적으로 준수해야 합니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>[국민청원] "식품 원산지 인증제 폐지 반대"&amp;nbsp;&amp;nbsp;전국매일신문</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 06:03:56 GMT</t>
+          <t>Tue, 13 Oct 2026 05:40:19 GMT</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOQWUxWURIZ1NGU2RDaExfd1lWemVGbFlsQlNRV3ViSjgyVm5YZFphYU1UUGk2NS1iblVjd3lUNGdzUjdSdU50S3ZmczRnUmQwbEJlekd0NkNycWdTbk16TmpXRXVQYmk4QWVpd25MN2FlSU9YVGpFX1BsZVRabFY4akN3WTJWWU40bUpwT2xKSkw3eXlF?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibkFVX3lxTE5kemRCZFZJQXppYUlTRmRCeTFLeGg3SklTbzNub1pVRlNPYUhjOUhWd1h4MlI2d3J5X2JMZ1ZydFBJVW1NV05Bb29IZXd2SGNlNmdiVDQzR3l5V0dnbnh2bjJYZkZuWVdhbEdmOXJn?oc=5</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="I31" t="inlineStr"/>
     </row>
@@ -1581,22 +1581,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>'믿고 찾았는데', 농협 하나로마트도 원산지 위반…70%가 강원도서 발생 - 머니투데이 - 머니투데이</t>
+          <t>어선 관리의 디지털화와 해산물 원산지 투명성 확보. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>'믿고 찾았는데', 농협 하나로마트도 원산지 위반…70%가 강원도서 발생 - 머니투데이&amp;nbsp;&amp;nbsp;머니투데이</t>
+          <t>어선 관리의 디지털화와 해산물 원산지 투명성 확보.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 00:10:28 GMT</t>
+          <t>Tue, 13 Oct 2026 09:58:44 GMT</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBCNGtuSl9wb0FOdE5RY18xTzdQRnFfQ0xDQ3RNSlZvX29nVEs4UHczZElYYW1jdm85WXEwdzZreUdMREpkdTlEbTVDSHFzX0Z5b0dJRWlDV1VOb29sbFhNbUJ5SVYxbUhqWmhpYV9HYlrSAXBBVV95cUxQQjRrbkpfcG9BTnROUWNfMU83UEZxX0NMQ0N0TUpWb19vZ1RLOFB3M2RJWGFtY3ZvOVlxMHc2a3lHTERKZHU5RG01Q0hxc19GeW9HSUVpQ1dVTm9vbGxYTW1CeUlWMW1IalpoaWFfR2Ja?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiggFBVV95cUxOTnNyWXdyX1RGdmpqcWp6LUpWbW9DRUlFNHB5QVlBclhsN0V3ZEJxcm1TaENPckZ5eVRKeDZxckMwT3BaWHVuUzh0T1FURUxoZ0EzMm54ZjdqNkJCaElFN1BNZ2RVS3NlRDE0dU1QRDFJVEMyQmwwNU03Y3V0ZmpvVWhR?oc=5</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I32" t="inlineStr"/>
     </row>
@@ -1618,108 +1618,182 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2027년부터 베트남 상품의 원산지 판정에 관한 새로운 규정이 적용될 예정입니다. - Vietnam.vn</t>
+          <t>'믿고 찾았는데', 농협 하나로마트도 원산지 위반…70%가 강원도서 발생 - 머니투데이 - 머니투데이</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>2027년부터 베트남 상품의 원산지 판정에 관한 새로운 규정이 적용될 예정입니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
+          <t>'믿고 찾았는데', 농협 하나로마트도 원산지 위반…70%가 강원도서 발생 - 머니투데이&amp;nbsp;&amp;nbsp;머니투데이</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 00:08:01 GMT</t>
+          <t>Tue, 13 Oct 2026 00:10:28 GMT</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS3dnTzVidWRHNXkzY3NSOEFabF9odE1PUnR4dlBsVUVhMVE0cFNicU9PNk1CbjVfcTBKN3Y3VnUzS0NiZUNyRUVaVFNDOTA2NEhscWhJZGFnM3FUM09aQU1aNkR2bHpEbDdPV0hVR1dZbjdIQm5FMzlpajdPVEpYZkFzb1o3ZXl3b3ZDTG1xOWo3SW8ySGQ0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMicEFVX3lxTFBCNGtuSl9wb0FOdE5RY18xTzdQRnFfQ0xDQ3RNSlZvX29nVEs4UHczZElYYW1jdm85WXEwdzZreUdMREpkdTlEbTVDSHFzX0Z5b0dJRWlDV1VOb29sbFhNbUJ5SVYxbUhqWmhpYV9HYlrSAXBBVV95cUxQQjRrbkpfcG9BTnROUWNfMU83UEZxX0NMQ0N0TUpWb19vZ1RLOFB3M2RJWGFtY3ZvOVlxMHc2a3lHTERKZHU5RG01Q0hxc19GeW9HSUVpQ1dVTm9vbGxYTW1CeUlWMW1IalpoaWFfR2Ja?oc=5</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>중</t>
+          <t>하</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>미국 중국과 '반도체 무역 전쟁'에 불리한 처지, 희토류와 광물 공급망 대체 어려워 - 비즈니스포스트</t>
+          <t>VIFTA 활용: 기업은 원산지 규정을 적극적으로 준수해야 합니다. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>미국 중국과 '반도체 무역 전쟁'에 불리한 처지, 희토류와 광물 공급망 대체 어려워&amp;nbsp;&amp;nbsp;비즈니스포스트</t>
+          <t>VIFTA 활용: 기업은 원산지 규정을 적극적으로 준수해야 합니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>Tue, 13 Oct 2026 05:36:36 GMT</t>
+          <t>Tue, 13 Oct 2026 06:03:56 GMT</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5HZTRPa3UzQXVIQTk4Q2JKdVQ0QzJGUU51VlN1NUNpTUk4ZlBxcGtweUctdS1pbFEtQmlhTm1lN3ROT2EtWVBZdFhjaEdmckFOeGRWbzIxQktudnBvcl82c3BhODQ1MXV4V3l5QVRnNHZWX1U?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilAFBVV95cUxOQWUxWURIZ1NGU2RDaExfd1lWemVGbFlsQlNRV3ViSjgyVm5YZFphYU1UUGk2NS1iblVjd3lUNGdzUjdSdU50S3ZmczRnUmQwbEJlekd0NkNycWdTbk16TmpXRXVQYmk4QWVpd25MN2FlSU9YVGpFX1BsZVRabFY4akN3WTJWWU40bUpwT2xKSkw3eXlF?oc=5</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>수출통제</t>
+          <t>원산지</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>세계 경유 공급난 확산…미국은 러시아산 수입 완화, 중국은 수출 통제 : 경제 - 재경일보</t>
+          <t>2027년부터 베트남 상품의 원산지 판정에 관한 새로운 규정이 적용될 예정입니다. - Vietnam.vn</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>세계 경유 공급난 확산…미국은 러시아산 수입 완화, 중국은 수출 통제 : 경제&amp;nbsp;&amp;nbsp;재경일보</t>
+          <t>2027년부터 베트남 상품의 원산지 판정에 관한 새로운 규정이 적용될 예정입니다.&amp;nbsp;&amp;nbsp;Vietnam.vn</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Mon, 12 Oct 2026 20:16:00 GMT</t>
+          <t>Tue, 13 Oct 2026 00:08:01 GMT</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1RMmRPbEJyZkkzNHZPLU83VnEwQmtYZGRNdF8zaTV0c3pfRUlWNnR2WE5xd0JQYnpjd3Fhc1pZTWJLQnE2V01aaU9NUQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS3dnTzVidWRHNXkzY3NSOEFabF9odE1PUnR4dlBsVUVhMVE0cFNicU9PNk1CbjVfcTBKN3Y3VnUzS0NiZUNyRUVaVFNDOTA2NEhscWhJZGFnM3FUM09aQU1aNkR2bHpEbDdPV0hVR1dZbjdIQm5FMzlpajdPVEpYZkFzb1o3ZXl3b3ZDTG1xOWo3SW8ySGQ0?oc=5</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>하</t>
+          <t>중</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>미국 중국과 '반도체 무역 전쟁'에 불리한 처지, 희토류와 광물 공급망 대체 어려워 - 비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>미국 중국과 '반도체 무역 전쟁'에 불리한 처지, 희토류와 광물 공급망 대체 어려워&amp;nbsp;&amp;nbsp;비즈니스포스트</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Tue, 13 Oct 2026 05:36:36 GMT</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMic0FVX3lxTE5HZTRPa3UzQXVIQTk4Q2JKdVQ0QzJGUU51VlN1NUNpTUk4ZlBxcGtweUctdS1pbFEtQmlhTm1lN3ROT2EtWVBZdFhjaEdmckFOeGRWbzIxQktudnBvcl82c3BhODQ1MXV4V3l5QVRnNHZWX1U?oc=5</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="n">
         <v>2</v>
       </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>수출통제</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>세계 경유 공급난 확산…미국은 러시아산 수입 완화, 중국은 수출 통제 : 경제 - 재경일보</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>세계 경유 공급난 확산…미국은 러시아산 수입 완화, 중국은 수출 통제 : 경제&amp;nbsp;&amp;nbsp;재경일보</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Mon, 12 Oct 2026 20:16:00 GMT</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiS0FVX3lxTE1RMmRPbEJyZkkzNHZPLU83VnEwQmtYZGRNdF8zaTV0c3pfRUlWNnR2WE5xd0JQYnpjd3Fhc1pZTWJLQnE2V01aaU9NUQ?oc=5</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="n">
+        <v>2</v>
+      </c>
+      <c r="I37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
